--- a/events/Prague_2019_WC/Prague_2019_WC_start.xlsx
+++ b/events/Prague_2019_WC/Prague_2019_WC_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W608"/>
+  <dimension ref="A1:AC607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1264,7 @@
           <t>MOORHOUSE Eoin</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>70052</t>
         </is>
@@ -1292,7 +1322,7 @@
           <t>KOTOV Pavel</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>66761</t>
         </is>
@@ -1350,7 +1380,7 @@
           <t>YERENGAIPOV Kuanysh</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>42085</t>
         </is>
@@ -1408,7 +1438,7 @@
           <t>TSAKMAKIS Christos</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>35433</t>
         </is>
@@ -1466,7 +1496,7 @@
           <t>XU Yongzhao</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>69446</t>
         </is>
@@ -1524,7 +1554,7 @@
           <t>ZOU Weijian</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>94208</t>
         </is>
@@ -1582,7 +1612,7 @@
           <t>LONG Tren</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>57124</t>
         </is>
@@ -1640,7 +1670,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -1698,7 +1728,7 @@
           <t>ECHANIZ Pau</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>75786</t>
         </is>
@@ -1756,7 +1786,7 @@
           <t>HUANG Fa</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>87703</t>
         </is>
@@ -1814,7 +1844,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -1872,7 +1902,7 @@
           <t>CARVALHO Jose</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>35486</t>
         </is>
@@ -1930,7 +1960,7 @@
           <t>KULIKOV Alexandr</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>39679</t>
         </is>
@@ -1988,7 +2018,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -2046,7 +2076,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -2104,7 +2134,7 @@
           <t>CORREA Charles</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
@@ -2162,7 +2192,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -2220,7 +2250,7 @@
           <t>LOWTHER Steven</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>44811</t>
         </is>
@@ -2278,7 +2308,7 @@
           <t>FERNANDEZ Luis</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>51851</t>
         </is>
@@ -2336,7 +2366,7 @@
           <t>KHRAMTSOV Dmitrii</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>66768</t>
         </is>
@@ -2394,7 +2424,7 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -2452,7 +2482,7 @@
           <t>TUCHSCHERER Lennard</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>60090</t>
         </is>
@@ -2510,7 +2540,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -2568,7 +2598,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -2626,7 +2656,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -2684,7 +2714,7 @@
           <t>SZTUBA Igor</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>35087</t>
         </is>
@@ -2742,7 +2772,7 @@
           <t>TRUMMER Timo</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>41599</t>
         </is>
@@ -2800,7 +2830,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -2858,7 +2888,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -2916,7 +2946,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -2974,7 +3004,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -3032,7 +3062,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -3090,7 +3120,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -3148,7 +3178,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -3206,7 +3236,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -3264,7 +3294,7 @@
           <t>SZTUBA Kacper</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
@@ -3322,7 +3352,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -3380,7 +3410,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -3438,7 +3468,7 @@
           <t>JOLY Cedric</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>35681</t>
         </is>
@@ -3496,7 +3526,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -3554,7 +3584,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -3612,7 +3642,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -3670,7 +3700,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -3728,7 +3758,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -3786,7 +3816,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -3844,7 +3874,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -3902,7 +3932,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -3960,7 +3990,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -4018,7 +4048,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -4076,7 +4106,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -4134,7 +4164,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -4192,7 +4222,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -4250,7 +4280,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -4308,7 +4338,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -4366,7 +4396,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -4424,7 +4454,7 @@
           <t>STACH Aleksandra</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>61261</t>
         </is>
@@ -4482,7 +4512,7 @@
           <t>SAETHER Mariann</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>53420</t>
         </is>
@@ -4540,7 +4570,7 @@
           <t>CRAIG Hannah</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>35815</t>
         </is>
@@ -4598,7 +4628,7 @@
           <t>ECHARRI Xanet</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>77339</t>
         </is>
@@ -4656,7 +4686,7 @@
           <t>COSTA Carmen</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>80546</t>
         </is>
@@ -4714,7 +4744,7 @@
           <t>XU Yanru</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>63801</t>
         </is>
@@ -4772,7 +4802,7 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>36936</t>
         </is>
@@ -4830,7 +4860,7 @@
           <t>KRIESINGER Janina</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>93682</t>
         </is>
@@ -4888,7 +4918,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -4946,7 +4976,7 @@
           <t>SEPRENYI Sara Timea</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>52211</t>
         </is>
@@ -5004,7 +5034,7 @@
           <t>SOUZA COSTA Marina</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>42972</t>
         </is>
@@ -5062,7 +5092,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -5120,7 +5150,7 @@
           <t>NICHOLAS Jane</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>93757</t>
         </is>
@@ -5178,7 +5208,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -5236,7 +5266,7 @@
           <t>THOMAS Hannah</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>85758</t>
         </is>
@@ -5294,7 +5324,7 @@
           <t>BRAENDLE Naemi</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>68845</t>
         </is>
@@ -5352,7 +5382,7 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -5410,7 +5440,7 @@
           <t>MINAZOVA Alsu</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>53314</t>
         </is>
@@ -5468,7 +5498,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -5526,7 +5556,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -5584,7 +5614,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -5642,7 +5672,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -5700,7 +5730,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -5758,7 +5788,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -5816,7 +5846,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -5874,7 +5904,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -5932,7 +5962,7 @@
           <t>JONES Selina</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>43475</t>
         </is>
@@ -5990,7 +6020,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -6048,7 +6078,7 @@
           <t>WERATSCHNIG Nina</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>41614</t>
         </is>
@@ -6106,7 +6136,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -6164,7 +6194,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -6222,7 +6252,7 @@
           <t>FABER Anna</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>39059</t>
         </is>
@@ -6280,7 +6310,7 @@
           <t>LI Tong</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>52023</t>
         </is>
@@ -6338,7 +6368,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -6396,7 +6426,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -6454,7 +6484,7 @@
           <t>MINTALOVA Eliska</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>56169</t>
         </is>
@@ -6512,7 +6542,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -6570,7 +6600,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -6628,7 +6658,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -6686,7 +6716,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -6744,7 +6774,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
+      <c r="X110" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -6802,7 +6832,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
+      <c r="X111" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -6860,7 +6890,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -6918,7 +6948,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -6976,7 +7006,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -7034,7 +7064,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -7092,7 +7122,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -7150,7 +7180,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -7208,7 +7238,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -7266,7 +7296,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -7324,7 +7354,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -7382,7 +7412,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -7440,7 +7470,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -7498,7 +7528,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
+      <c r="X123" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -7556,7 +7586,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
+      <c r="X124" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -7614,7 +7644,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
+      <c r="X125" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -7672,7 +7702,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
+      <c r="X126" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -7730,7 +7760,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="X127" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -7788,7 +7818,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="X128" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -7846,7 +7876,7 @@
           <t>MOORHOUSE Eoin</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>70052</t>
         </is>
@@ -7904,7 +7934,7 @@
           <t>KOTOV Pavel</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>66761</t>
         </is>
@@ -7962,7 +7992,7 @@
           <t>YERENGAIPOV Kuanysh</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>42085</t>
         </is>
@@ -8020,7 +8050,7 @@
           <t>TSAKMAKIS Christos</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>35433</t>
         </is>
@@ -8078,7 +8108,7 @@
           <t>XU Yongzhao</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>69446</t>
         </is>
@@ -8136,7 +8166,7 @@
           <t>ZOU Weijian</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>94208</t>
         </is>
@@ -8194,7 +8224,7 @@
           <t>LONG Tren</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>57124</t>
         </is>
@@ -8252,7 +8282,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -8310,7 +8340,7 @@
           <t>ECHANIZ Pau</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>75786</t>
         </is>
@@ -8368,7 +8398,7 @@
           <t>HUANG Fa</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="X138" t="inlineStr">
         <is>
           <t>87703</t>
         </is>
@@ -8426,7 +8456,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -8484,7 +8514,7 @@
           <t>CARVALHO Jose</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>35486</t>
         </is>
@@ -8542,7 +8572,7 @@
           <t>KULIKOV Alexandr</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>39679</t>
         </is>
@@ -8600,7 +8630,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -8658,7 +8688,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
+      <c r="X143" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -8716,7 +8746,7 @@
           <t>CORREA Charles</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
@@ -8774,7 +8804,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -8832,7 +8862,7 @@
           <t>LOWTHER Steven</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
+      <c r="X146" t="inlineStr">
         <is>
           <t>44811</t>
         </is>
@@ -8890,7 +8920,7 @@
           <t>FERNANDEZ Luis</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>51851</t>
         </is>
@@ -8948,7 +8978,7 @@
           <t>KHRAMTSOV Dmitrii</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>66768</t>
         </is>
@@ -9006,7 +9036,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -9064,7 +9094,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="X150" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -9122,7 +9152,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -9180,7 +9210,7 @@
           <t>SZTUBA Igor</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
+      <c r="X152" t="inlineStr">
         <is>
           <t>35087</t>
         </is>
@@ -9238,7 +9268,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
+      <c r="X153" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -9296,7 +9326,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="X154" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -9354,7 +9384,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -9412,7 +9442,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="X156" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -9470,7 +9500,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
+      <c r="X157" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -9528,7 +9558,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
+      <c r="X158" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -9586,7 +9616,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="X159" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -9644,7 +9674,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -9702,7 +9732,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
+      <c r="X161" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -9760,7 +9790,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -9818,7 +9848,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr">
+      <c r="X163" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -9876,7 +9906,7 @@
           <t>STACH Aleksandra</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>61261</t>
         </is>
@@ -9934,7 +9964,7 @@
           <t>SAETHER Mariann</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
+      <c r="X165" t="inlineStr">
         <is>
           <t>53420</t>
         </is>
@@ -9992,7 +10022,7 @@
           <t>CRAIG Hannah</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
+      <c r="X166" t="inlineStr">
         <is>
           <t>35815</t>
         </is>
@@ -10050,7 +10080,7 @@
           <t>ECHARRI Xanet</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="X167" t="inlineStr">
         <is>
           <t>77339</t>
         </is>
@@ -10108,7 +10138,7 @@
           <t>COSTA Carmen</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>80546</t>
         </is>
@@ -10166,7 +10196,7 @@
           <t>XU Yanru</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr">
+      <c r="X169" t="inlineStr">
         <is>
           <t>63801</t>
         </is>
@@ -10224,7 +10254,7 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="X170" t="inlineStr">
         <is>
           <t>36936</t>
         </is>
@@ -10282,7 +10312,7 @@
           <t>KRIESINGER Janina</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>93682</t>
         </is>
@@ -10340,7 +10370,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="X172" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -10398,7 +10428,7 @@
           <t>SEPRENYI Sara Timea</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
+      <c r="X173" t="inlineStr">
         <is>
           <t>52211</t>
         </is>
@@ -10456,7 +10486,7 @@
           <t>SOUZA COSTA Marina</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="X174" t="inlineStr">
         <is>
           <t>42972</t>
         </is>
@@ -10514,7 +10544,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -10572,7 +10602,7 @@
           <t>NICHOLAS Jane</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
+      <c r="X176" t="inlineStr">
         <is>
           <t>93757</t>
         </is>
@@ -10630,7 +10660,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -10688,7 +10718,7 @@
           <t>THOMAS Hannah</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
+      <c r="X178" t="inlineStr">
         <is>
           <t>85758</t>
         </is>
@@ -10746,7 +10776,7 @@
           <t>BRAENDLE Naemi</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>68845</t>
         </is>
@@ -10804,7 +10834,7 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
+      <c r="X180" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -10862,7 +10892,7 @@
           <t>MINAZOVA Alsu</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
+      <c r="X181" t="inlineStr">
         <is>
           <t>53314</t>
         </is>
@@ -10920,7 +10950,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -10978,7 +11008,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr">
+      <c r="X183" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -11036,7 +11066,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="X184" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -11094,7 +11124,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -11152,7 +11182,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -11210,7 +11240,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
+      <c r="X187" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -11268,7 +11298,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -11326,7 +11356,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr">
+      <c r="X189" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -11384,7 +11414,7 @@
           <t>JONES Selina</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
+      <c r="X190" t="inlineStr">
         <is>
           <t>43475</t>
         </is>
@@ -11442,7 +11472,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="X191" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -11500,7 +11530,7 @@
           <t>WERATSCHNIG Nina</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="X192" t="inlineStr">
         <is>
           <t>41614</t>
         </is>
@@ -11558,7 +11588,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
+      <c r="X193" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -11616,7 +11646,7 @@
           <t>FABER Anna</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="X194" t="inlineStr">
         <is>
           <t>39059</t>
         </is>
@@ -11674,7 +11704,7 @@
           <t>LI Tong</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>52023</t>
         </is>
@@ -11732,7 +11762,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
+      <c r="X196" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -11790,7 +11820,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
+      <c r="X197" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -11848,7 +11878,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
+      <c r="X198" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -11906,7 +11936,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="X199" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -11964,7 +11994,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
+      <c r="X200" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -12022,7 +12052,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
+      <c r="X201" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -12080,7 +12110,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -12138,7 +12168,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
+      <c r="X203" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -12461,7 +12491,7 @@
           <t>NICHOLAS Jane</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>93757</t>
         </is>
@@ -12519,7 +12549,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
+      <c r="X210" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -12577,7 +12607,7 @@
           <t>SOUZA COSTA Marina</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>42972</t>
         </is>
@@ -12635,7 +12665,7 @@
           <t>YU Cuishan</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr">
+      <c r="X212" t="inlineStr">
         <is>
           <t>75380</t>
         </is>
@@ -12693,7 +12723,7 @@
           <t>SCHMID Julia</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
+      <c r="X213" t="inlineStr">
         <is>
           <t>85991</t>
         </is>
@@ -12751,7 +12781,7 @@
           <t>ECHARRI Xanet</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>77339</t>
         </is>
@@ -12809,7 +12839,7 @@
           <t>TENG Qianqian</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="X215" t="inlineStr">
         <is>
           <t>94209</t>
         </is>
@@ -12867,7 +12897,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
+      <c r="X216" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -12925,7 +12955,7 @@
           <t>SATO Ayano</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>60374</t>
         </is>
@@ -12983,7 +13013,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
+      <c r="X218" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -13041,7 +13071,7 @@
           <t>NOVAK Lea</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
+      <c r="X219" t="inlineStr">
         <is>
           <t>60323</t>
         </is>
@@ -13099,7 +13129,7 @@
           <t>MISHIMA Ren</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr">
+      <c r="X220" t="inlineStr">
         <is>
           <t>37757</t>
         </is>
@@ -13157,7 +13187,7 @@
           <t>JAKOB Zoe</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
+      <c r="X221" t="inlineStr">
         <is>
           <t>77246</t>
         </is>
@@ -13215,7 +13245,7 @@
           <t>THOMAS Hannah</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>85758</t>
         </is>
@@ -13273,7 +13303,7 @@
           <t>BERNERT Anne</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
+      <c r="X223" t="inlineStr">
         <is>
           <t>77248</t>
         </is>
@@ -13331,7 +13361,7 @@
           <t>YAGI Airi</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
+      <c r="X224" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
@@ -13389,7 +13419,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
+      <c r="X225" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -13447,7 +13477,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
+      <c r="X226" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -13505,7 +13535,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
+      <c r="X227" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -13563,7 +13593,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U228" t="inlineStr">
+      <c r="X228" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -13621,7 +13651,7 @@
           <t>BORGHI Elena</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr">
+      <c r="X229" t="inlineStr">
         <is>
           <t>75493</t>
         </is>
@@ -13679,7 +13709,7 @@
           <t>STACH Aleksandra</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>61261</t>
         </is>
@@ -13737,7 +13767,7 @@
           <t>LUKNAROVA Emanuela</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
+      <c r="X231" t="inlineStr">
         <is>
           <t>76973</t>
         </is>
@@ -13795,7 +13825,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U232" t="inlineStr">
+      <c r="X232" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -13853,7 +13883,7 @@
           <t>DONNELLY Sage</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr">
+      <c r="X233" t="inlineStr">
         <is>
           <t>60119</t>
         </is>
@@ -13911,7 +13941,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr">
+      <c r="X234" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -13969,7 +13999,7 @@
           <t>RIHOVA Eva</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>51791</t>
         </is>
@@ -14027,7 +14057,7 @@
           <t>HAVLICKOVA Katerina</t>
         </is>
       </c>
-      <c r="U236" t="inlineStr">
+      <c r="X236" t="inlineStr">
         <is>
           <t>35048</t>
         </is>
@@ -14085,7 +14115,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U237" t="inlineStr">
+      <c r="X237" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -14143,7 +14173,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr">
+      <c r="X238" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -14201,7 +14231,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="X239" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -14259,7 +14289,7 @@
           <t>OGILVIE Sophie</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>53134</t>
         </is>
@@ -14317,7 +14347,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -14375,7 +14405,7 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -14433,7 +14463,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -14491,7 +14521,7 @@
           <t>MINAZOVA Alsu</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>53314</t>
         </is>
@@ -14549,7 +14579,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -14607,7 +14637,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
+      <c r="X246" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -14665,7 +14695,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr">
+      <c r="X247" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -14723,7 +14753,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
+      <c r="X248" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -14781,7 +14811,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr">
+      <c r="X249" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -14839,7 +14869,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
+      <c r="X250" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -14897,7 +14927,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U251" t="inlineStr">
+      <c r="X251" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -14955,7 +14985,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
+      <c r="X252" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -15013,7 +15043,7 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
-      <c r="U253" t="inlineStr">
+      <c r="X253" t="inlineStr">
         <is>
           <t>42016</t>
         </is>
@@ -15071,7 +15101,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
+      <c r="X254" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -15129,7 +15159,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U255" t="inlineStr">
+      <c r="X255" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -15187,7 +15217,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
+      <c r="X256" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -15245,7 +15275,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -15303,7 +15333,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="X258" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -15361,7 +15391,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
+      <c r="X259" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -15419,7 +15449,7 @@
           <t>TUGCU Tarik</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>51845</t>
         </is>
@@ -15477,7 +15507,7 @@
           <t>KARLIVANS Toms</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
+      <c r="X261" t="inlineStr">
         <is>
           <t>52325</t>
         </is>
@@ -15535,7 +15565,7 @@
           <t>CHEN Tianlu</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
+      <c r="X262" t="inlineStr">
         <is>
           <t>84748</t>
         </is>
@@ -15593,7 +15623,7 @@
           <t>ERTEK Yusuf</t>
         </is>
       </c>
-      <c r="U263" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>55173</t>
         </is>
@@ -15651,7 +15681,7 @@
           <t>CELMINS Ritvars</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
+      <c r="X264" t="inlineStr">
         <is>
           <t>35182</t>
         </is>
@@ -15709,7 +15739,7 @@
           <t>OCHOA Manuel</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
+      <c r="X265" t="inlineStr">
         <is>
           <t>69081</t>
         </is>
@@ -15767,7 +15797,7 @@
           <t>ACAR Mustafa Arda</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
+      <c r="X266" t="inlineStr">
         <is>
           <t>73572</t>
         </is>
@@ -15825,7 +15855,7 @@
           <t>DE COSTER Gabriel</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
+      <c r="X267" t="inlineStr">
         <is>
           <t>68818</t>
         </is>
@@ -15883,7 +15913,7 @@
           <t>MCCREERY Alistair</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
+      <c r="X268" t="inlineStr">
         <is>
           <t>60125</t>
         </is>
@@ -15941,7 +15971,7 @@
           <t>KANAYA Tohru</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
+      <c r="X269" t="inlineStr">
         <is>
           <t>36484</t>
         </is>
@@ -15999,7 +16029,7 @@
           <t>STANOVSKY Samuel</t>
         </is>
       </c>
-      <c r="U270" t="inlineStr">
+      <c r="X270" t="inlineStr">
         <is>
           <t>84121</t>
         </is>
@@ -16057,7 +16087,7 @@
           <t>HENDRICK Noel</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
+      <c r="X271" t="inlineStr">
         <is>
           <t>43003</t>
         </is>
@@ -16115,7 +16145,7 @@
           <t>ALVARENGA Frederico</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr">
+      <c r="X272" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
@@ -16173,7 +16203,7 @@
           <t>TEAGUE Eoin</t>
         </is>
       </c>
-      <c r="U273" t="inlineStr">
+      <c r="X273" t="inlineStr">
         <is>
           <t>37913</t>
         </is>
@@ -16231,7 +16261,7 @@
           <t>ECHANIZ Pau</t>
         </is>
       </c>
-      <c r="U274" t="inlineStr">
+      <c r="X274" t="inlineStr">
         <is>
           <t>75786</t>
         </is>
@@ -16289,7 +16319,7 @@
           <t>WESTFALL Tyler</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>51919</t>
         </is>
@@ -16347,7 +16377,7 @@
           <t>KARLSSON Max</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
+      <c r="X276" t="inlineStr">
         <is>
           <t>35111</t>
         </is>
@@ -16405,7 +16435,7 @@
           <t>KORPES Ren</t>
         </is>
       </c>
-      <c r="U277" t="inlineStr">
+      <c r="X277" t="inlineStr">
         <is>
           <t>39941</t>
         </is>
@@ -16463,7 +16493,7 @@
           <t>MAIMISTOV Sergey</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
+      <c r="X278" t="inlineStr">
         <is>
           <t>53267</t>
         </is>
@@ -16521,7 +16551,7 @@
           <t>JOSEPH Joshua</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
+      <c r="X279" t="inlineStr">
         <is>
           <t>69141</t>
         </is>
@@ -16579,7 +16609,7 @@
           <t>RODRIGUES Guilherme</t>
         </is>
       </c>
-      <c r="U280" t="inlineStr">
+      <c r="X280" t="inlineStr">
         <is>
           <t>60486</t>
         </is>
@@ -16637,7 +16667,7 @@
           <t>GUBENKO Nikita</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr">
+      <c r="X281" t="inlineStr">
         <is>
           <t>39130</t>
         </is>
@@ -16695,7 +16725,7 @@
           <t>NABASKUES Unai</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr">
+      <c r="X282" t="inlineStr">
         <is>
           <t>38775</t>
         </is>
@@ -16753,7 +16783,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U283" t="inlineStr">
+      <c r="X283" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -16811,7 +16841,7 @@
           <t>STANOVSKY Martin</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>68782</t>
         </is>
@@ -16869,7 +16899,7 @@
           <t>PESTOV Ruslan</t>
         </is>
       </c>
-      <c r="U285" t="inlineStr">
+      <c r="X285" t="inlineStr">
         <is>
           <t>36138</t>
         </is>
@@ -16927,7 +16957,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U286" t="inlineStr">
+      <c r="X286" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -16985,7 +17015,7 @@
           <t>RODRIGUES Fabio</t>
         </is>
       </c>
-      <c r="U287" t="inlineStr">
+      <c r="X287" t="inlineStr">
         <is>
           <t>38023</t>
         </is>
@@ -17043,7 +17073,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U288" t="inlineStr">
+      <c r="X288" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -17101,7 +17131,7 @@
           <t>BOLG Leo</t>
         </is>
       </c>
-      <c r="U289" t="inlineStr">
+      <c r="X289" t="inlineStr">
         <is>
           <t>43470</t>
         </is>
@@ -17159,7 +17189,7 @@
           <t>QUAN Xin</t>
         </is>
       </c>
-      <c r="U290" t="inlineStr">
+      <c r="X290" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
@@ -17217,7 +17247,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U291" t="inlineStr">
+      <c r="X291" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -17275,7 +17305,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U292" t="inlineStr">
+      <c r="X292" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -17333,7 +17363,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr">
+      <c r="X293" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -17391,7 +17421,7 @@
           <t>DANGEN Jack</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
+      <c r="X294" t="inlineStr">
         <is>
           <t>51865</t>
         </is>
@@ -17449,7 +17479,7 @@
           <t>BEDA Marcello</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
+      <c r="X295" t="inlineStr">
         <is>
           <t>39899</t>
         </is>
@@ -17507,7 +17537,7 @@
           <t>STAHL Lukas</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
+      <c r="X296" t="inlineStr">
         <is>
           <t>55115</t>
         </is>
@@ -17565,7 +17595,7 @@
           <t>MUNSCH Manuel</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr">
+      <c r="X297" t="inlineStr">
         <is>
           <t>35631</t>
         </is>
@@ -17623,7 +17653,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
+      <c r="X298" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -17681,7 +17711,7 @@
           <t>MAJERCZAK Krzysztof</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="X299" t="inlineStr">
         <is>
           <t>53647</t>
         </is>
@@ -17739,7 +17769,7 @@
           <t>YAZAWA Kazuki</t>
         </is>
       </c>
-      <c r="U300" t="inlineStr">
+      <c r="X300" t="inlineStr">
         <is>
           <t>36482</t>
         </is>
@@ -17797,7 +17827,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U301" t="inlineStr">
+      <c r="X301" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -17855,7 +17885,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
+      <c r="X302" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -17913,7 +17943,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U303" t="inlineStr">
+      <c r="X303" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -17971,7 +18001,7 @@
           <t>BURGI Quentin</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
+      <c r="X304" t="inlineStr">
         <is>
           <t>41590</t>
         </is>
@@ -18029,7 +18059,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U305" t="inlineStr">
+      <c r="X305" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -18087,7 +18117,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U306" t="inlineStr">
+      <c r="X306" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -18145,7 +18175,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U307" t="inlineStr">
+      <c r="X307" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -18203,7 +18233,7 @@
           <t>TESTEN Niko</t>
         </is>
       </c>
-      <c r="U308" t="inlineStr">
+      <c r="X308" t="inlineStr">
         <is>
           <t>39980</t>
         </is>
@@ -18261,7 +18291,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U309" t="inlineStr">
+      <c r="X309" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -18319,7 +18349,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U310" t="inlineStr">
+      <c r="X310" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -18377,7 +18407,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U311" t="inlineStr">
+      <c r="X311" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -18435,7 +18465,7 @@
           <t>BOWERS Christopher</t>
         </is>
       </c>
-      <c r="U312" t="inlineStr">
+      <c r="X312" t="inlineStr">
         <is>
           <t>52010</t>
         </is>
@@ -18493,7 +18523,7 @@
           <t>ANDERSON Timothy</t>
         </is>
       </c>
-      <c r="U313" t="inlineStr">
+      <c r="X313" t="inlineStr">
         <is>
           <t>38432</t>
         </is>
@@ -18551,7 +18581,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U314" t="inlineStr">
+      <c r="X314" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -18609,7 +18639,7 @@
           <t>MADORE Mathurin</t>
         </is>
       </c>
-      <c r="U315" t="inlineStr">
+      <c r="X315" t="inlineStr">
         <is>
           <t>51994</t>
         </is>
@@ -18667,7 +18697,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U316" t="inlineStr">
+      <c r="X316" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -18725,7 +18755,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U317" t="inlineStr">
+      <c r="X317" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -18783,7 +18813,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U318" t="inlineStr">
+      <c r="X318" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -18841,7 +18871,7 @@
           <t>HENGST Stefan</t>
         </is>
       </c>
-      <c r="U319" t="inlineStr">
+      <c r="X319" t="inlineStr">
         <is>
           <t>39061</t>
         </is>
@@ -18899,7 +18929,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U320" t="inlineStr">
+      <c r="X320" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -18957,7 +18987,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U321" t="inlineStr">
+      <c r="X321" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -19015,7 +19045,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U322" t="inlineStr">
+      <c r="X322" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -19073,7 +19103,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U323" t="inlineStr">
+      <c r="X323" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -19131,7 +19161,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
+      <c r="X324" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -19189,7 +19219,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U325" t="inlineStr">
+      <c r="X325" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -19247,7 +19277,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr">
+      <c r="X326" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -19305,7 +19335,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U327" t="inlineStr">
+      <c r="X327" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -19363,7 +19393,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U328" t="inlineStr">
+      <c r="X328" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -19421,7 +19451,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="X329" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -19479,7 +19509,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U330" t="inlineStr">
+      <c r="X330" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -19537,7 +19567,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U331" t="inlineStr">
+      <c r="X331" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -19595,7 +19625,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr">
+      <c r="X332" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -19653,7 +19683,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U333" t="inlineStr">
+      <c r="X333" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -19711,7 +19741,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U334" t="inlineStr">
+      <c r="X334" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -19769,7 +19799,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U335" t="inlineStr">
+      <c r="X335" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -19827,7 +19857,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U336" t="inlineStr">
+      <c r="X336" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -19885,7 +19915,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U337" t="inlineStr">
+      <c r="X337" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -19943,7 +19973,7 @@
           <t>NICHOLAS Jane</t>
         </is>
       </c>
-      <c r="U338" t="inlineStr">
+      <c r="X338" t="inlineStr">
         <is>
           <t>93757</t>
         </is>
@@ -20001,7 +20031,7 @@
           <t>SOUZA COSTA Marina</t>
         </is>
       </c>
-      <c r="U339" t="inlineStr">
+      <c r="X339" t="inlineStr">
         <is>
           <t>42972</t>
         </is>
@@ -20059,7 +20089,7 @@
           <t>YU Cuishan</t>
         </is>
       </c>
-      <c r="U340" t="inlineStr">
+      <c r="X340" t="inlineStr">
         <is>
           <t>75380</t>
         </is>
@@ -20117,7 +20147,7 @@
           <t>SCHMID Julia</t>
         </is>
       </c>
-      <c r="U341" t="inlineStr">
+      <c r="X341" t="inlineStr">
         <is>
           <t>85991</t>
         </is>
@@ -20175,7 +20205,7 @@
           <t>ECHARRI Xanet</t>
         </is>
       </c>
-      <c r="U342" t="inlineStr">
+      <c r="X342" t="inlineStr">
         <is>
           <t>77339</t>
         </is>
@@ -20233,7 +20263,7 @@
           <t>TENG Qianqian</t>
         </is>
       </c>
-      <c r="U343" t="inlineStr">
+      <c r="X343" t="inlineStr">
         <is>
           <t>94209</t>
         </is>
@@ -20291,7 +20321,7 @@
           <t>SATO Ayano</t>
         </is>
       </c>
-      <c r="U344" t="inlineStr">
+      <c r="X344" t="inlineStr">
         <is>
           <t>60374</t>
         </is>
@@ -20349,7 +20379,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr">
+      <c r="X345" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -20407,7 +20437,7 @@
           <t>NOVAK Lea</t>
         </is>
       </c>
-      <c r="U346" t="inlineStr">
+      <c r="X346" t="inlineStr">
         <is>
           <t>60323</t>
         </is>
@@ -20465,7 +20495,7 @@
           <t>MISHIMA Ren</t>
         </is>
       </c>
-      <c r="U347" t="inlineStr">
+      <c r="X347" t="inlineStr">
         <is>
           <t>37757</t>
         </is>
@@ -20523,7 +20553,7 @@
           <t>THOMAS Hannah</t>
         </is>
       </c>
-      <c r="U348" t="inlineStr">
+      <c r="X348" t="inlineStr">
         <is>
           <t>85758</t>
         </is>
@@ -20581,7 +20611,7 @@
           <t>BERNERT Anne</t>
         </is>
       </c>
-      <c r="U349" t="inlineStr">
+      <c r="X349" t="inlineStr">
         <is>
           <t>77248</t>
         </is>
@@ -20639,7 +20669,7 @@
           <t>YAGI Airi</t>
         </is>
       </c>
-      <c r="U350" t="inlineStr">
+      <c r="X350" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
@@ -20697,7 +20727,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U351" t="inlineStr">
+      <c r="X351" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -20755,7 +20785,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U352" t="inlineStr">
+      <c r="X352" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -20813,7 +20843,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U353" t="inlineStr">
+      <c r="X353" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -20871,7 +20901,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U354" t="inlineStr">
+      <c r="X354" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -20929,7 +20959,7 @@
           <t>BORGHI Elena</t>
         </is>
       </c>
-      <c r="U355" t="inlineStr">
+      <c r="X355" t="inlineStr">
         <is>
           <t>75493</t>
         </is>
@@ -20987,7 +21017,7 @@
           <t>STACH Aleksandra</t>
         </is>
       </c>
-      <c r="U356" t="inlineStr">
+      <c r="X356" t="inlineStr">
         <is>
           <t>61261</t>
         </is>
@@ -21045,7 +21075,7 @@
           <t>LUKNAROVA Emanuela</t>
         </is>
       </c>
-      <c r="U357" t="inlineStr">
+      <c r="X357" t="inlineStr">
         <is>
           <t>76973</t>
         </is>
@@ -21103,7 +21133,7 @@
           <t>DONNELLY Sage</t>
         </is>
       </c>
-      <c r="U358" t="inlineStr">
+      <c r="X358" t="inlineStr">
         <is>
           <t>60119</t>
         </is>
@@ -21161,7 +21191,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U359" t="inlineStr">
+      <c r="X359" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -21219,7 +21249,7 @@
           <t>HAVLICKOVA Katerina</t>
         </is>
       </c>
-      <c r="U360" t="inlineStr">
+      <c r="X360" t="inlineStr">
         <is>
           <t>35048</t>
         </is>
@@ -21277,7 +21307,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U361" t="inlineStr">
+      <c r="X361" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -21335,7 +21365,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U362" t="inlineStr">
+      <c r="X362" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -21393,7 +21423,7 @@
           <t>OGILVIE Sophie</t>
         </is>
       </c>
-      <c r="U363" t="inlineStr">
+      <c r="X363" t="inlineStr">
         <is>
           <t>53134</t>
         </is>
@@ -21451,7 +21481,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U364" t="inlineStr">
+      <c r="X364" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -21509,7 +21539,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U365" t="inlineStr">
+      <c r="X365" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -21567,7 +21597,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U366" t="inlineStr">
+      <c r="X366" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -21625,7 +21655,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U367" t="inlineStr">
+      <c r="X367" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -21683,7 +21713,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U368" t="inlineStr">
+      <c r="X368" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -21741,7 +21771,7 @@
           <t>TUGCU Tarik</t>
         </is>
       </c>
-      <c r="U369" t="inlineStr">
+      <c r="X369" t="inlineStr">
         <is>
           <t>51845</t>
         </is>
@@ -21799,7 +21829,7 @@
           <t>KARLIVANS Toms</t>
         </is>
       </c>
-      <c r="U370" t="inlineStr">
+      <c r="X370" t="inlineStr">
         <is>
           <t>52325</t>
         </is>
@@ -21857,7 +21887,7 @@
           <t>CHEN Tianlu</t>
         </is>
       </c>
-      <c r="U371" t="inlineStr">
+      <c r="X371" t="inlineStr">
         <is>
           <t>84748</t>
         </is>
@@ -21915,7 +21945,7 @@
           <t>ERTEK Yusuf</t>
         </is>
       </c>
-      <c r="U372" t="inlineStr">
+      <c r="X372" t="inlineStr">
         <is>
           <t>55173</t>
         </is>
@@ -21973,7 +22003,7 @@
           <t>CELMINS Ritvars</t>
         </is>
       </c>
-      <c r="U373" t="inlineStr">
+      <c r="X373" t="inlineStr">
         <is>
           <t>35182</t>
         </is>
@@ -22031,7 +22061,7 @@
           <t>OCHOA Manuel</t>
         </is>
       </c>
-      <c r="U374" t="inlineStr">
+      <c r="X374" t="inlineStr">
         <is>
           <t>69081</t>
         </is>
@@ -22089,7 +22119,7 @@
           <t>ACAR Mustafa Arda</t>
         </is>
       </c>
-      <c r="U375" t="inlineStr">
+      <c r="X375" t="inlineStr">
         <is>
           <t>73572</t>
         </is>
@@ -22147,7 +22177,7 @@
           <t>DE COSTER Gabriel</t>
         </is>
       </c>
-      <c r="U376" t="inlineStr">
+      <c r="X376" t="inlineStr">
         <is>
           <t>68818</t>
         </is>
@@ -22205,7 +22235,7 @@
           <t>MCCREERY Alistair</t>
         </is>
       </c>
-      <c r="U377" t="inlineStr">
+      <c r="X377" t="inlineStr">
         <is>
           <t>60125</t>
         </is>
@@ -22263,7 +22293,7 @@
           <t>KANAYA Tohru</t>
         </is>
       </c>
-      <c r="U378" t="inlineStr">
+      <c r="X378" t="inlineStr">
         <is>
           <t>36484</t>
         </is>
@@ -22321,7 +22351,7 @@
           <t>STANOVSKY Samuel</t>
         </is>
       </c>
-      <c r="U379" t="inlineStr">
+      <c r="X379" t="inlineStr">
         <is>
           <t>84121</t>
         </is>
@@ -22379,7 +22409,7 @@
           <t>HENDRICK Noel</t>
         </is>
       </c>
-      <c r="U380" t="inlineStr">
+      <c r="X380" t="inlineStr">
         <is>
           <t>43003</t>
         </is>
@@ -22437,7 +22467,7 @@
           <t>ALVARENGA Frederico</t>
         </is>
       </c>
-      <c r="U381" t="inlineStr">
+      <c r="X381" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
@@ -22495,7 +22525,7 @@
           <t>TEAGUE Eoin</t>
         </is>
       </c>
-      <c r="U382" t="inlineStr">
+      <c r="X382" t="inlineStr">
         <is>
           <t>37913</t>
         </is>
@@ -22553,7 +22583,7 @@
           <t>ECHANIZ Pau</t>
         </is>
       </c>
-      <c r="U383" t="inlineStr">
+      <c r="X383" t="inlineStr">
         <is>
           <t>75786</t>
         </is>
@@ -22611,7 +22641,7 @@
           <t>WESTFALL Tyler</t>
         </is>
       </c>
-      <c r="U384" t="inlineStr">
+      <c r="X384" t="inlineStr">
         <is>
           <t>51919</t>
         </is>
@@ -22669,7 +22699,7 @@
           <t>KARLSSON Max</t>
         </is>
       </c>
-      <c r="U385" t="inlineStr">
+      <c r="X385" t="inlineStr">
         <is>
           <t>35111</t>
         </is>
@@ -22727,7 +22757,7 @@
           <t>KORPES Ren</t>
         </is>
       </c>
-      <c r="U386" t="inlineStr">
+      <c r="X386" t="inlineStr">
         <is>
           <t>39941</t>
         </is>
@@ -22785,7 +22815,7 @@
           <t>MAIMISTOV Sergey</t>
         </is>
       </c>
-      <c r="U387" t="inlineStr">
+      <c r="X387" t="inlineStr">
         <is>
           <t>53267</t>
         </is>
@@ -22843,7 +22873,7 @@
           <t>JOSEPH Joshua</t>
         </is>
       </c>
-      <c r="U388" t="inlineStr">
+      <c r="X388" t="inlineStr">
         <is>
           <t>69141</t>
         </is>
@@ -22901,7 +22931,7 @@
           <t>RODRIGUES Guilherme</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr">
+      <c r="X389" t="inlineStr">
         <is>
           <t>60486</t>
         </is>
@@ -22959,7 +22989,7 @@
           <t>GUBENKO Nikita</t>
         </is>
       </c>
-      <c r="U390" t="inlineStr">
+      <c r="X390" t="inlineStr">
         <is>
           <t>39130</t>
         </is>
@@ -23017,7 +23047,7 @@
           <t>NABASKUES Unai</t>
         </is>
       </c>
-      <c r="U391" t="inlineStr">
+      <c r="X391" t="inlineStr">
         <is>
           <t>38775</t>
         </is>
@@ -23075,7 +23105,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U392" t="inlineStr">
+      <c r="X392" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -23133,7 +23163,7 @@
           <t>STANOVSKY Martin</t>
         </is>
       </c>
-      <c r="U393" t="inlineStr">
+      <c r="X393" t="inlineStr">
         <is>
           <t>68782</t>
         </is>
@@ -23191,7 +23221,7 @@
           <t>PESTOV Ruslan</t>
         </is>
       </c>
-      <c r="U394" t="inlineStr">
+      <c r="X394" t="inlineStr">
         <is>
           <t>36138</t>
         </is>
@@ -23249,7 +23279,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U395" t="inlineStr">
+      <c r="X395" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -23307,7 +23337,7 @@
           <t>RODRIGUES Fabio</t>
         </is>
       </c>
-      <c r="U396" t="inlineStr">
+      <c r="X396" t="inlineStr">
         <is>
           <t>38023</t>
         </is>
@@ -23365,7 +23395,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U397" t="inlineStr">
+      <c r="X397" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -23423,7 +23453,7 @@
           <t>BOLG Leo</t>
         </is>
       </c>
-      <c r="U398" t="inlineStr">
+      <c r="X398" t="inlineStr">
         <is>
           <t>43470</t>
         </is>
@@ -23481,7 +23511,7 @@
           <t>QUAN Xin</t>
         </is>
       </c>
-      <c r="U399" t="inlineStr">
+      <c r="X399" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
@@ -23539,7 +23569,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U400" t="inlineStr">
+      <c r="X400" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -23597,7 +23627,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U401" t="inlineStr">
+      <c r="X401" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -23655,7 +23685,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U402" t="inlineStr">
+      <c r="X402" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -23713,7 +23743,7 @@
           <t>DANGEN Jack</t>
         </is>
       </c>
-      <c r="U403" t="inlineStr">
+      <c r="X403" t="inlineStr">
         <is>
           <t>51865</t>
         </is>
@@ -23771,7 +23801,7 @@
           <t>BEDA Marcello</t>
         </is>
       </c>
-      <c r="U404" t="inlineStr">
+      <c r="X404" t="inlineStr">
         <is>
           <t>39899</t>
         </is>
@@ -23829,7 +23859,7 @@
           <t>MUNSCH Manuel</t>
         </is>
       </c>
-      <c r="U405" t="inlineStr">
+      <c r="X405" t="inlineStr">
         <is>
           <t>35631</t>
         </is>
@@ -23887,7 +23917,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U406" t="inlineStr">
+      <c r="X406" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -23945,7 +23975,7 @@
           <t>YAZAWA Kazuki</t>
         </is>
       </c>
-      <c r="U407" t="inlineStr">
+      <c r="X407" t="inlineStr">
         <is>
           <t>36482</t>
         </is>
@@ -24003,7 +24033,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U408" t="inlineStr">
+      <c r="X408" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -24061,7 +24091,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U409" t="inlineStr">
+      <c r="X409" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -24119,7 +24149,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U410" t="inlineStr">
+      <c r="X410" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -24177,7 +24207,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U411" t="inlineStr">
+      <c r="X411" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -24235,7 +24265,7 @@
           <t>ANDERSON Timothy</t>
         </is>
       </c>
-      <c r="U412" t="inlineStr">
+      <c r="X412" t="inlineStr">
         <is>
           <t>38432</t>
         </is>
@@ -24293,7 +24323,7 @@
           <t>MADORE Mathurin</t>
         </is>
       </c>
-      <c r="U413" t="inlineStr">
+      <c r="X413" t="inlineStr">
         <is>
           <t>51994</t>
         </is>
@@ -24351,7 +24381,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U414" t="inlineStr">
+      <c r="X414" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -24409,7 +24439,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U415" t="inlineStr">
+      <c r="X415" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -24467,7 +24497,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U416" t="inlineStr">
+      <c r="X416" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -25174,7 +25204,7 @@
           <t>KOTOV Pavel</t>
         </is>
       </c>
-      <c r="U430" t="inlineStr">
+      <c r="X430" t="inlineStr">
         <is>
           <t>66761</t>
         </is>
@@ -25232,7 +25262,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U431" t="inlineStr">
+      <c r="X431" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -25290,7 +25320,7 @@
           <t>KHRAMTSOV Dmitrii</t>
         </is>
       </c>
-      <c r="U432" t="inlineStr">
+      <c r="X432" t="inlineStr">
         <is>
           <t>66768</t>
         </is>
@@ -25348,7 +25378,7 @@
           <t>LOWTHER Steven</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
+      <c r="X433" t="inlineStr">
         <is>
           <t>44811</t>
         </is>
@@ -25406,7 +25436,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U434" t="inlineStr">
+      <c r="X434" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -25464,7 +25494,7 @@
           <t>CORREA Charles</t>
         </is>
       </c>
-      <c r="U435" t="inlineStr">
+      <c r="X435" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
@@ -25522,7 +25552,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U436" t="inlineStr">
+      <c r="X436" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -25580,7 +25610,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U437" t="inlineStr">
+      <c r="X437" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -25638,7 +25668,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U438" t="inlineStr">
+      <c r="X438" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -25696,7 +25726,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U439" t="inlineStr">
+      <c r="X439" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -25754,7 +25784,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr">
+      <c r="X440" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -25812,7 +25842,7 @@
           <t>TRUMMER Timo</t>
         </is>
       </c>
-      <c r="U441" t="inlineStr">
+      <c r="X441" t="inlineStr">
         <is>
           <t>41599</t>
         </is>
@@ -25870,7 +25900,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U442" t="inlineStr">
+      <c r="X442" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -25928,7 +25958,7 @@
           <t>TUCHSCHERER Lennard</t>
         </is>
       </c>
-      <c r="U443" t="inlineStr">
+      <c r="X443" t="inlineStr">
         <is>
           <t>60090</t>
         </is>
@@ -25986,7 +26016,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U444" t="inlineStr">
+      <c r="X444" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -26044,7 +26074,7 @@
           <t>JOLY Cedric</t>
         </is>
       </c>
-      <c r="U445" t="inlineStr">
+      <c r="X445" t="inlineStr">
         <is>
           <t>35681</t>
         </is>
@@ -26102,7 +26132,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U446" t="inlineStr">
+      <c r="X446" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -26160,7 +26190,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U447" t="inlineStr">
+      <c r="X447" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -26218,7 +26248,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U448" t="inlineStr">
+      <c r="X448" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -26276,7 +26306,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U449" t="inlineStr">
+      <c r="X449" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -26334,7 +26364,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U450" t="inlineStr">
+      <c r="X450" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -26392,7 +26422,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U451" t="inlineStr">
+      <c r="X451" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -26450,7 +26480,7 @@
           <t>SZTUBA Kacper</t>
         </is>
       </c>
-      <c r="U452" t="inlineStr">
+      <c r="X452" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
@@ -26508,7 +26538,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U453" t="inlineStr">
+      <c r="X453" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -26566,7 +26596,7 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U454" t="inlineStr">
+      <c r="X454" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -26624,7 +26654,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U455" t="inlineStr">
+      <c r="X455" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -26682,7 +26712,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U456" t="inlineStr">
+      <c r="X456" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -26740,7 +26770,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U457" t="inlineStr">
+      <c r="X457" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -26798,7 +26828,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U458" t="inlineStr">
+      <c r="X458" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -26856,7 +26886,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U459" t="inlineStr">
+      <c r="X459" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -26914,7 +26944,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U460" t="inlineStr">
+      <c r="X460" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -26972,7 +27002,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U461" t="inlineStr">
+      <c r="X461" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -27030,7 +27060,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U462" t="inlineStr">
+      <c r="X462" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -27088,7 +27118,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U463" t="inlineStr">
+      <c r="X463" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -27146,7 +27176,7 @@
           <t>FABER Anna</t>
         </is>
       </c>
-      <c r="U464" t="inlineStr">
+      <c r="X464" t="inlineStr">
         <is>
           <t>39059</t>
         </is>
@@ -27204,7 +27234,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U465" t="inlineStr">
+      <c r="X465" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -27262,7 +27292,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U466" t="inlineStr">
+      <c r="X466" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -27320,7 +27350,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U467" t="inlineStr">
+      <c r="X467" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -27378,7 +27408,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U468" t="inlineStr">
+      <c r="X468" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -27436,7 +27466,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U469" t="inlineStr">
+      <c r="X469" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -27494,7 +27524,7 @@
           <t>MINTALOVA Eliska</t>
         </is>
       </c>
-      <c r="U470" t="inlineStr">
+      <c r="X470" t="inlineStr">
         <is>
           <t>56169</t>
         </is>
@@ -27552,7 +27582,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U471" t="inlineStr">
+      <c r="X471" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -27610,7 +27640,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U472" t="inlineStr">
+      <c r="X472" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -27668,7 +27698,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U473" t="inlineStr">
+      <c r="X473" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -27726,7 +27756,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U474" t="inlineStr">
+      <c r="X474" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -27784,7 +27814,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U475" t="inlineStr">
+      <c r="X475" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -27842,7 +27872,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U476" t="inlineStr">
+      <c r="X476" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -27900,7 +27930,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U477" t="inlineStr">
+      <c r="X477" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -27958,7 +27988,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U478" t="inlineStr">
+      <c r="X478" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -28016,7 +28046,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U479" t="inlineStr">
+      <c r="X479" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -28074,7 +28104,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U480" t="inlineStr">
+      <c r="X480" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -28132,7 +28162,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U481" t="inlineStr">
+      <c r="X481" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -28190,7 +28220,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U482" t="inlineStr">
+      <c r="X482" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -28248,7 +28278,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U483" t="inlineStr">
+      <c r="X483" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -28306,7 +28336,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U484" t="inlineStr">
+      <c r="X484" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -28364,7 +28394,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U485" t="inlineStr">
+      <c r="X485" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -28422,7 +28452,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U486" t="inlineStr">
+      <c r="X486" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -28480,7 +28510,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U487" t="inlineStr">
+      <c r="X487" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -28538,7 +28568,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U488" t="inlineStr">
+      <c r="X488" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -28596,7 +28626,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U489" t="inlineStr">
+      <c r="X489" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -28664,7 +28694,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U490" t="inlineStr">
+      <c r="X490" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -28732,7 +28762,7 @@
           <t>SZTUBA Kacper</t>
         </is>
       </c>
-      <c r="U491" t="inlineStr">
+      <c r="X491" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
@@ -28800,7 +28830,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U492" t="inlineStr">
+      <c r="X492" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -28868,7 +28898,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U493" t="inlineStr">
+      <c r="X493" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -28936,7 +28966,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U494" t="inlineStr">
+      <c r="X494" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -29004,7 +29034,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U495" t="inlineStr">
+      <c r="X495" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -29072,7 +29102,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U496" t="inlineStr">
+      <c r="X496" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -29140,7 +29170,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U497" t="inlineStr">
+      <c r="X497" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -29208,7 +29238,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U498" t="inlineStr">
+      <c r="X498" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -29276,7 +29306,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U499" t="inlineStr">
+      <c r="X499" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -29344,7 +29374,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U500" t="inlineStr">
+      <c r="X500" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -29412,7 +29442,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U501" t="inlineStr">
+      <c r="X501" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -29480,7 +29510,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U502" t="inlineStr">
+      <c r="X502" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -29548,7 +29578,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U503" t="inlineStr">
+      <c r="X503" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -29616,7 +29646,7 @@
           <t>MINTALOVA Eliska</t>
         </is>
       </c>
-      <c r="U504" t="inlineStr">
+      <c r="X504" t="inlineStr">
         <is>
           <t>56169</t>
         </is>
@@ -29684,7 +29714,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U505" t="inlineStr">
+      <c r="X505" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -29752,7 +29782,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U506" t="inlineStr">
+      <c r="X506" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -29820,7 +29850,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U507" t="inlineStr">
+      <c r="X507" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -29888,7 +29918,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U508" t="inlineStr">
+      <c r="X508" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -29956,7 +29986,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U509" t="inlineStr">
+      <c r="X509" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -30226,7 +30256,7 @@
           <t>STACH Aleksandra</t>
         </is>
       </c>
-      <c r="U514" t="inlineStr">
+      <c r="X514" t="inlineStr">
         <is>
           <t>61261</t>
         </is>
@@ -30284,7 +30314,7 @@
           <t>NOVAK Lea</t>
         </is>
       </c>
-      <c r="U515" t="inlineStr">
+      <c r="X515" t="inlineStr">
         <is>
           <t>60323</t>
         </is>
@@ -30342,7 +30372,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U516" t="inlineStr">
+      <c r="X516" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -30400,7 +30430,7 @@
           <t>BORGHI Elena</t>
         </is>
       </c>
-      <c r="U517" t="inlineStr">
+      <c r="X517" t="inlineStr">
         <is>
           <t>75493</t>
         </is>
@@ -30458,7 +30488,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U518" t="inlineStr">
+      <c r="X518" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -30516,7 +30546,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U519" t="inlineStr">
+      <c r="X519" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -30574,7 +30604,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U520" t="inlineStr">
+      <c r="X520" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -30632,7 +30662,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U521" t="inlineStr">
+      <c r="X521" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -30690,7 +30720,7 @@
           <t>OGILVIE Sophie</t>
         </is>
       </c>
-      <c r="U522" t="inlineStr">
+      <c r="X522" t="inlineStr">
         <is>
           <t>53134</t>
         </is>
@@ -30748,7 +30778,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U523" t="inlineStr">
+      <c r="X523" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -30806,7 +30836,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U524" t="inlineStr">
+      <c r="X524" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -30864,7 +30894,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U525" t="inlineStr">
+      <c r="X525" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -30922,7 +30952,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U526" t="inlineStr">
+      <c r="X526" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -30980,7 +31010,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U527" t="inlineStr">
+      <c r="X527" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -31038,7 +31068,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U528" t="inlineStr">
+      <c r="X528" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -31096,7 +31126,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U529" t="inlineStr">
+      <c r="X529" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -31154,7 +31184,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U530" t="inlineStr">
+      <c r="X530" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -31212,7 +31242,7 @@
           <t>JAKOB Zoe</t>
         </is>
       </c>
-      <c r="U531" t="inlineStr">
+      <c r="X531" t="inlineStr">
         <is>
           <t>77246</t>
         </is>
@@ -31270,7 +31300,7 @@
           <t>RIHOVA Eva</t>
         </is>
       </c>
-      <c r="U532" t="inlineStr">
+      <c r="X532" t="inlineStr">
         <is>
           <t>51791</t>
         </is>
@@ -31328,7 +31358,7 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U533" t="inlineStr">
+      <c r="X533" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -31386,7 +31416,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U534" t="inlineStr">
+      <c r="X534" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -31444,7 +31474,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U535" t="inlineStr">
+      <c r="X535" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -31502,7 +31532,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U536" t="inlineStr">
+      <c r="X536" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -31560,7 +31590,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U537" t="inlineStr">
+      <c r="X537" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -31618,7 +31648,7 @@
           <t>MINAZOVA Alsu</t>
         </is>
       </c>
-      <c r="U538" t="inlineStr">
+      <c r="X538" t="inlineStr">
         <is>
           <t>53314</t>
         </is>
@@ -31676,7 +31706,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U539" t="inlineStr">
+      <c r="X539" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -31734,7 +31764,7 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
-      <c r="U540" t="inlineStr">
+      <c r="X540" t="inlineStr">
         <is>
           <t>42016</t>
         </is>
@@ -31792,7 +31822,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U541" t="inlineStr">
+      <c r="X541" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -31850,7 +31880,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U542" t="inlineStr">
+      <c r="X542" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -31908,7 +31938,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U543" t="inlineStr">
+      <c r="X543" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -31966,7 +31996,7 @@
           <t>TEAGUE Eoin</t>
         </is>
       </c>
-      <c r="U544" t="inlineStr">
+      <c r="X544" t="inlineStr">
         <is>
           <t>37913</t>
         </is>
@@ -32024,7 +32054,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U545" t="inlineStr">
+      <c r="X545" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -32082,7 +32112,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U546" t="inlineStr">
+      <c r="X546" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -32140,7 +32170,7 @@
           <t>QUAN Xin</t>
         </is>
       </c>
-      <c r="U547" t="inlineStr">
+      <c r="X547" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
@@ -32198,7 +32228,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U548" t="inlineStr">
+      <c r="X548" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -32256,7 +32286,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U549" t="inlineStr">
+      <c r="X549" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -32314,7 +32344,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U550" t="inlineStr">
+      <c r="X550" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -32372,7 +32402,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U551" t="inlineStr">
+      <c r="X551" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -32430,7 +32460,7 @@
           <t>MADORE Mathurin</t>
         </is>
       </c>
-      <c r="U552" t="inlineStr">
+      <c r="X552" t="inlineStr">
         <is>
           <t>51994</t>
         </is>
@@ -32488,7 +32518,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U553" t="inlineStr">
+      <c r="X553" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -32497,7 +32527,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -32512,7 +32542,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>Heats</t>
+          <t>Semifinal</t>
         </is>
       </c>
       <c r="F554" t="inlineStr">
@@ -32527,12 +32557,12 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>10:24:00</t>
+          <t>10:24:59</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="J554" t="n">
@@ -32543,12 +32573,12 @@
       </c>
       <c r="R554" t="inlineStr">
         <is>
-          <t>NEE Ashley</t>
-        </is>
-      </c>
-      <c r="U554" t="inlineStr">
-        <is>
-          <t>36363</t>
+          <t>BUTCHER Finn</t>
+        </is>
+      </c>
+      <c r="X554" t="inlineStr">
+        <is>
+          <t>36663</t>
         </is>
       </c>
     </row>
@@ -32585,28 +32615,28 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>10:24:59</t>
+          <t>10:26:59</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="J555" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K555" t="n">
         <v>554</v>
       </c>
       <c r="R555" t="inlineStr">
         <is>
-          <t>BUTCHER Finn</t>
-        </is>
-      </c>
-      <c r="U555" t="inlineStr">
-        <is>
-          <t>36663</t>
+          <t>OSCHMAUTZ Felix</t>
+        </is>
+      </c>
+      <c r="X555" t="inlineStr">
+        <is>
+          <t>51856</t>
         </is>
       </c>
     </row>
@@ -32643,28 +32673,28 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>10:26:59</t>
+          <t>10:28:58</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>SLO</t>
         </is>
       </c>
       <c r="J556" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K556" t="n">
         <v>555</v>
       </c>
       <c r="R556" t="inlineStr">
         <is>
-          <t>OSCHMAUTZ Felix</t>
-        </is>
-      </c>
-      <c r="U556" t="inlineStr">
-        <is>
-          <t>51856</t>
+          <t>SRABOTNIK Martin</t>
+        </is>
+      </c>
+      <c r="X556" t="inlineStr">
+        <is>
+          <t>39080</t>
         </is>
       </c>
     </row>
@@ -32701,28 +32731,28 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>10:28:58</t>
+          <t>10:31:00</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="J557" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K557" t="n">
         <v>556</v>
       </c>
       <c r="R557" t="inlineStr">
         <is>
-          <t>SRABOTNIK Martin</t>
-        </is>
-      </c>
-      <c r="U557" t="inlineStr">
-        <is>
-          <t>39080</t>
+          <t>GONCALVES Pedro</t>
+        </is>
+      </c>
+      <c r="X557" t="inlineStr">
+        <is>
+          <t>38017</t>
         </is>
       </c>
     </row>
@@ -32759,28 +32789,28 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>10:31:00</t>
+          <t>10:32:59</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="J558" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="K558" t="n">
         <v>557</v>
       </c>
       <c r="R558" t="inlineStr">
         <is>
-          <t>GONCALVES Pedro</t>
-        </is>
-      </c>
-      <c r="U558" t="inlineStr">
-        <is>
-          <t>38017</t>
+          <t>PASIUT Michal</t>
+        </is>
+      </c>
+      <c r="X558" t="inlineStr">
+        <is>
+          <t>35095</t>
         </is>
       </c>
     </row>
@@ -32817,7 +32847,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>10:32:59</t>
+          <t>10:35:00</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -32826,19 +32856,19 @@
         </is>
       </c>
       <c r="J559" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="K559" t="n">
         <v>558</v>
       </c>
       <c r="R559" t="inlineStr">
         <is>
-          <t>PASIUT Michal</t>
-        </is>
-      </c>
-      <c r="U559" t="inlineStr">
-        <is>
-          <t>35095</t>
+          <t>MAJERCZAK Krzysztof</t>
+        </is>
+      </c>
+      <c r="X559" t="inlineStr">
+        <is>
+          <t>53647</t>
         </is>
       </c>
     </row>
@@ -32875,28 +32905,28 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>10:35:00</t>
+          <t>10:37:00</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J560" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K560" t="n">
         <v>559</v>
       </c>
       <c r="R560" t="inlineStr">
         <is>
-          <t>MAJERCZAK Krzysztof</t>
-        </is>
-      </c>
-      <c r="U560" t="inlineStr">
-        <is>
-          <t>53647</t>
+          <t>STAHL Lukas</t>
+        </is>
+      </c>
+      <c r="X560" t="inlineStr">
+        <is>
+          <t>55115</t>
         </is>
       </c>
     </row>
@@ -32933,28 +32963,28 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>10:37:00</t>
+          <t>10:39:00</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="J561" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="K561" t="n">
         <v>560</v>
       </c>
       <c r="R561" t="inlineStr">
         <is>
-          <t>STAHL Lukas</t>
-        </is>
-      </c>
-      <c r="U561" t="inlineStr">
-        <is>
-          <t>55115</t>
+          <t>IVALDI Zeno</t>
+        </is>
+      </c>
+      <c r="X561" t="inlineStr">
+        <is>
+          <t>35480</t>
         </is>
       </c>
     </row>
@@ -32991,28 +33021,28 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>10:39:00</t>
+          <t>10:41:01</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="J562" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="K562" t="n">
         <v>561</v>
       </c>
       <c r="R562" t="inlineStr">
         <is>
-          <t>IVALDI Zeno</t>
-        </is>
-      </c>
-      <c r="U562" t="inlineStr">
-        <is>
-          <t>35480</t>
+          <t>POPIELA Dariusz</t>
+        </is>
+      </c>
+      <c r="X562" t="inlineStr">
+        <is>
+          <t>35096</t>
         </is>
       </c>
     </row>
@@ -33049,28 +33079,28 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>10:41:01</t>
+          <t>10:42:59</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>SUI</t>
         </is>
       </c>
       <c r="J563" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K563" t="n">
         <v>562</v>
       </c>
       <c r="R563" t="inlineStr">
         <is>
-          <t>POPIELA Dariusz</t>
-        </is>
-      </c>
-      <c r="U563" t="inlineStr">
-        <is>
-          <t>35096</t>
+          <t>WERRO Lukas</t>
+        </is>
+      </c>
+      <c r="X563" t="inlineStr">
+        <is>
+          <t>35347</t>
         </is>
       </c>
     </row>
@@ -33107,28 +33137,28 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>10:42:59</t>
+          <t>10:45:01</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t>SUI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="J564" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K564" t="n">
         <v>563</v>
       </c>
       <c r="R564" t="inlineStr">
         <is>
-          <t>WERRO Lukas</t>
-        </is>
-      </c>
-      <c r="U564" t="inlineStr">
-        <is>
-          <t>35347</t>
+          <t>LAUNAY Antoine</t>
+        </is>
+      </c>
+      <c r="X564" t="inlineStr">
+        <is>
+          <t>68776</t>
         </is>
       </c>
     </row>
@@ -33165,28 +33195,28 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>10:45:01</t>
+          <t>10:46:58</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J565" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="K565" t="n">
         <v>564</v>
       </c>
       <c r="R565" t="inlineStr">
         <is>
-          <t>LAUNAY Antoine</t>
-        </is>
-      </c>
-      <c r="U565" t="inlineStr">
-        <is>
-          <t>68776</t>
+          <t>BURGI Quentin</t>
+        </is>
+      </c>
+      <c r="X565" t="inlineStr">
+        <is>
+          <t>41590</t>
         </is>
       </c>
     </row>
@@ -33223,28 +33253,28 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>10:46:58</t>
+          <t>10:49:00</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="J566" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K566" t="n">
         <v>565</v>
       </c>
       <c r="R566" t="inlineStr">
         <is>
-          <t>BURGI Quentin</t>
-        </is>
-      </c>
-      <c r="U566" t="inlineStr">
-        <is>
-          <t>41590</t>
+          <t>LEITNER Mario</t>
+        </is>
+      </c>
+      <c r="X566" t="inlineStr">
+        <is>
+          <t>35546</t>
         </is>
       </c>
     </row>
@@ -33281,28 +33311,28 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>10:49:00</t>
+          <t>10:50:59</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J567" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K567" t="n">
         <v>566</v>
       </c>
       <c r="R567" t="inlineStr">
         <is>
-          <t>LEITNER Mario</t>
-        </is>
-      </c>
-      <c r="U567" t="inlineStr">
-        <is>
-          <t>35546</t>
+          <t>MALEK Andrej</t>
+        </is>
+      </c>
+      <c r="X567" t="inlineStr">
+        <is>
+          <t>39246</t>
         </is>
       </c>
     </row>
@@ -33339,28 +33369,28 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>10:50:59</t>
+          <t>10:52:59</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="J568" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="K568" t="n">
         <v>567</v>
       </c>
       <c r="R568" t="inlineStr">
         <is>
-          <t>MALEK Andrej</t>
-        </is>
-      </c>
-      <c r="U568" t="inlineStr">
-        <is>
-          <t>39246</t>
+          <t>DELFOUR Lucien</t>
+        </is>
+      </c>
+      <c r="X568" t="inlineStr">
+        <is>
+          <t>36537</t>
         </is>
       </c>
     </row>
@@ -33397,28 +33427,28 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>10:52:59</t>
+          <t>10:55:00</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="J569" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="K569" t="n">
         <v>568</v>
       </c>
       <c r="R569" t="inlineStr">
         <is>
-          <t>DELFOUR Lucien</t>
-        </is>
-      </c>
-      <c r="U569" t="inlineStr">
-        <is>
-          <t>36537</t>
+          <t>BOWERS Christopher</t>
+        </is>
+      </c>
+      <c r="X569" t="inlineStr">
+        <is>
+          <t>52010</t>
         </is>
       </c>
     </row>
@@ -33455,28 +33485,28 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>10:55:00</t>
+          <t>10:57:01</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>SLO</t>
         </is>
       </c>
       <c r="J570" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K570" t="n">
         <v>569</v>
       </c>
       <c r="R570" t="inlineStr">
         <is>
-          <t>BOWERS Christopher</t>
-        </is>
-      </c>
-      <c r="U570" t="inlineStr">
-        <is>
-          <t>52010</t>
+          <t>TESTEN Niko</t>
+        </is>
+      </c>
+      <c r="X570" t="inlineStr">
+        <is>
+          <t>39980</t>
         </is>
       </c>
     </row>
@@ -33513,28 +33543,28 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>10:57:01</t>
+          <t>10:59:00</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="J571" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="K571" t="n">
         <v>570</v>
       </c>
       <c r="R571" t="inlineStr">
         <is>
-          <t>TESTEN Niko</t>
-        </is>
-      </c>
-      <c r="U571" t="inlineStr">
-        <is>
-          <t>39980</t>
+          <t>SMOLEN Michal</t>
+        </is>
+      </c>
+      <c r="X571" t="inlineStr">
+        <is>
+          <t>36397</t>
         </is>
       </c>
     </row>
@@ -33571,28 +33601,28 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>10:59:00</t>
+          <t>11:01:00</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>SUI</t>
         </is>
       </c>
       <c r="J572" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K572" t="n">
         <v>571</v>
       </c>
       <c r="R572" t="inlineStr">
         <is>
-          <t>SMOLEN Michal</t>
-        </is>
-      </c>
-      <c r="U572" t="inlineStr">
-        <is>
-          <t>36397</t>
+          <t>DOUGOUD Martin</t>
+        </is>
+      </c>
+      <c r="X572" t="inlineStr">
+        <is>
+          <t>35426</t>
         </is>
       </c>
     </row>
@@ -33629,28 +33659,28 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>11:01:00</t>
+          <t>11:03:02</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
         <is>
-          <t>SUI</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J573" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K573" t="n">
         <v>572</v>
       </c>
       <c r="R573" t="inlineStr">
         <is>
-          <t>DOUGOUD Martin</t>
-        </is>
-      </c>
-      <c r="U573" t="inlineStr">
-        <is>
-          <t>35426</t>
+          <t>EIGEL Pavel</t>
+        </is>
+      </c>
+      <c r="X573" t="inlineStr">
+        <is>
+          <t>35458</t>
         </is>
       </c>
     </row>
@@ -33687,28 +33717,28 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>11:03:02</t>
+          <t>11:05:00</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J574" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="K574" t="n">
         <v>573</v>
       </c>
       <c r="R574" t="inlineStr">
         <is>
-          <t>EIGEL Pavel</t>
-        </is>
-      </c>
-      <c r="U574" t="inlineStr">
-        <is>
-          <t>35458</t>
+          <t>PRINDIS Vit</t>
+        </is>
+      </c>
+      <c r="X574" t="inlineStr">
+        <is>
+          <t>35065</t>
         </is>
       </c>
     </row>
@@ -33745,28 +33775,28 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>11:05:00</t>
+          <t>11:06:57</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J575" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="K575" t="n">
         <v>574</v>
       </c>
       <c r="R575" t="inlineStr">
         <is>
-          <t>PRINDIS Vit</t>
-        </is>
-      </c>
-      <c r="U575" t="inlineStr">
-        <is>
-          <t>35065</t>
+          <t>HENGST Stefan</t>
+        </is>
+      </c>
+      <c r="X575" t="inlineStr">
+        <is>
+          <t>39061</t>
         </is>
       </c>
     </row>
@@ -33803,28 +33833,28 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>11:06:57</t>
+          <t>11:09:00</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="J576" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K576" t="n">
         <v>575</v>
       </c>
       <c r="R576" t="inlineStr">
         <is>
-          <t>HENGST Stefan</t>
-        </is>
-      </c>
-      <c r="U576" t="inlineStr">
-        <is>
-          <t>39061</t>
+          <t>OHRSTROM Isak</t>
+        </is>
+      </c>
+      <c r="X576" t="inlineStr">
+        <is>
+          <t>35101</t>
         </is>
       </c>
     </row>
@@ -33861,28 +33891,28 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>11:09:00</t>
+          <t>11:10:59</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="J577" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="K577" t="n">
         <v>576</v>
       </c>
       <c r="R577" t="inlineStr">
         <is>
-          <t>OHRSTROM Isak</t>
-        </is>
-      </c>
-      <c r="U577" t="inlineStr">
-        <is>
-          <t>35101</t>
+          <t>CLARKE Joseph</t>
+        </is>
+      </c>
+      <c r="X577" t="inlineStr">
+        <is>
+          <t>35654</t>
         </is>
       </c>
     </row>
@@ -33919,28 +33949,28 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>11:10:59</t>
+          <t>11:13:00</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J578" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K578" t="n">
         <v>577</v>
       </c>
       <c r="R578" t="inlineStr">
         <is>
-          <t>CLARKE Joseph</t>
-        </is>
-      </c>
-      <c r="U578" t="inlineStr">
-        <is>
-          <t>35654</t>
+          <t>NEVEU Boris</t>
+        </is>
+      </c>
+      <c r="X578" t="inlineStr">
+        <is>
+          <t>35396</t>
         </is>
       </c>
     </row>
@@ -33977,28 +34007,28 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>11:13:00</t>
+          <t>11:14:58</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="J579" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K579" t="n">
         <v>578</v>
       </c>
       <c r="R579" t="inlineStr">
         <is>
-          <t>NEVEU Boris</t>
-        </is>
-      </c>
-      <c r="U579" t="inlineStr">
-        <is>
-          <t>35396</t>
+          <t>DE GENNARO Giovanni</t>
+        </is>
+      </c>
+      <c r="X579" t="inlineStr">
+        <is>
+          <t>35244</t>
         </is>
       </c>
     </row>
@@ -34035,28 +34065,28 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>11:14:58</t>
+          <t>11:17:00</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="J580" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K580" t="n">
         <v>579</v>
       </c>
       <c r="R580" t="inlineStr">
         <is>
-          <t>DE GENNARO Giovanni</t>
-        </is>
-      </c>
-      <c r="U580" t="inlineStr">
-        <is>
-          <t>35244</t>
+          <t>FORBES-CRYANS Bradley</t>
+        </is>
+      </c>
+      <c r="X580" t="inlineStr">
+        <is>
+          <t>36513</t>
         </is>
       </c>
     </row>
@@ -34093,28 +34123,28 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>11:17:00</t>
+          <t>11:18:59</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J581" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K581" t="n">
         <v>580</v>
       </c>
       <c r="R581" t="inlineStr">
         <is>
-          <t>FORBES-CRYANS Bradley</t>
-        </is>
-      </c>
-      <c r="U581" t="inlineStr">
-        <is>
-          <t>36513</t>
+          <t>PRSKAVEC Jiri</t>
+        </is>
+      </c>
+      <c r="X581" t="inlineStr">
+        <is>
+          <t>35033</t>
         </is>
       </c>
     </row>
@@ -34151,7 +34181,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>11:18:59</t>
+          <t>11:21:00</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -34160,19 +34190,19 @@
         </is>
       </c>
       <c r="J582" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="K582" t="n">
         <v>581</v>
       </c>
       <c r="R582" t="inlineStr">
         <is>
-          <t>PRSKAVEC Jiri</t>
-        </is>
-      </c>
-      <c r="U582" t="inlineStr">
-        <is>
-          <t>35033</t>
+          <t>HRADILEK Vavrinec</t>
+        </is>
+      </c>
+      <c r="X582" t="inlineStr">
+        <is>
+          <t>35031</t>
         </is>
       </c>
     </row>
@@ -34209,35 +34239,35 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>11:21:00</t>
+          <t>11:23:01</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J583" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="K583" t="n">
         <v>582</v>
       </c>
       <c r="R583" t="inlineStr">
         <is>
-          <t>HRADILEK Vavrinec</t>
-        </is>
-      </c>
-      <c r="U583" t="inlineStr">
-        <is>
-          <t>35031</t>
+          <t>GRIGAR Jakub</t>
+        </is>
+      </c>
+      <c r="X583" t="inlineStr">
+        <is>
+          <t>37284</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -34247,12 +34277,12 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>Semifinal</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F584" t="inlineStr">
@@ -34267,28 +34297,38 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>11:23:01</t>
+          <t>12:02:59</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J584" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K584" t="n">
         <v>583</v>
       </c>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N584" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="R584" t="inlineStr">
         <is>
-          <t>GRIGAR Jakub</t>
-        </is>
-      </c>
-      <c r="U584" t="inlineStr">
-        <is>
-          <t>37284</t>
+          <t>MINAZOVA Alsu</t>
+        </is>
+      </c>
+      <c r="X584" t="inlineStr">
+        <is>
+          <t>53314</t>
         </is>
       </c>
     </row>
@@ -34325,38 +34365,38 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>12:02:59</t>
+          <t>12:05:59</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="J585" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K585" t="n">
         <v>584</v>
       </c>
       <c r="M585" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N585" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R585" t="inlineStr">
         <is>
-          <t>MINAZOVA Alsu</t>
-        </is>
-      </c>
-      <c r="U585" t="inlineStr">
-        <is>
-          <t>53314</t>
+          <t>CHEN Shi</t>
+        </is>
+      </c>
+      <c r="X585" t="inlineStr">
+        <is>
+          <t>52027</t>
         </is>
       </c>
     </row>
@@ -34393,38 +34433,38 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>12:05:59</t>
+          <t>12:08:59</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="J586" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="K586" t="n">
         <v>585</v>
       </c>
       <c r="M586" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N586" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R586" t="inlineStr">
         <is>
-          <t>CHEN Shi</t>
-        </is>
-      </c>
-      <c r="U586" t="inlineStr">
-        <is>
-          <t>52027</t>
+          <t>LEIBFARTH Evy</t>
+        </is>
+      </c>
+      <c r="X586" t="inlineStr">
+        <is>
+          <t>83538</t>
         </is>
       </c>
     </row>
@@ -34461,38 +34501,38 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>12:08:59</t>
+          <t>12:11:59</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="J587" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="K587" t="n">
         <v>586</v>
       </c>
       <c r="M587" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N587" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R587" t="inlineStr">
         <is>
-          <t>LEIBFARTH Evy</t>
-        </is>
-      </c>
-      <c r="U587" t="inlineStr">
-        <is>
-          <t>83538</t>
+          <t>FOX Noemie</t>
+        </is>
+      </c>
+      <c r="X587" t="inlineStr">
+        <is>
+          <t>44812</t>
         </is>
       </c>
     </row>
@@ -34529,38 +34569,38 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>12:11:59</t>
+          <t>12:14:59</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J588" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K588" t="n">
         <v>587</v>
       </c>
       <c r="M588" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N588" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R588" t="inlineStr">
         <is>
-          <t>FOX Noemie</t>
-        </is>
-      </c>
-      <c r="U588" t="inlineStr">
-        <is>
-          <t>44812</t>
+          <t>BAUDU Lucie</t>
+        </is>
+      </c>
+      <c r="X588" t="inlineStr">
+        <is>
+          <t>35669</t>
         </is>
       </c>
     </row>
@@ -34597,38 +34637,38 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>12:14:59</t>
+          <t>12:20:01</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="J589" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K589" t="n">
         <v>588</v>
       </c>
       <c r="M589" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N589" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R589" t="inlineStr">
         <is>
-          <t>BAUDU Lucie</t>
-        </is>
-      </c>
-      <c r="U589" t="inlineStr">
-        <is>
-          <t>35669</t>
+          <t>WERATSCHNIG Nadine</t>
+        </is>
+      </c>
+      <c r="X589" t="inlineStr">
+        <is>
+          <t>41613</t>
         </is>
       </c>
     </row>
@@ -34665,38 +34705,38 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>12:20:01</t>
+          <t>12:22:59</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J590" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K590" t="n">
         <v>589</v>
       </c>
       <c r="M590" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N590" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R590" t="inlineStr">
         <is>
-          <t>WERATSCHNIG Nadine</t>
-        </is>
-      </c>
-      <c r="U590" t="inlineStr">
-        <is>
-          <t>41613</t>
+          <t>FISEROVA Tereza</t>
+        </is>
+      </c>
+      <c r="X590" t="inlineStr">
+        <is>
+          <t>42016</t>
         </is>
       </c>
     </row>
@@ -34733,38 +34773,38 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>12:22:59</t>
+          <t>12:26:00</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="J591" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K591" t="n">
         <v>590</v>
       </c>
       <c r="M591" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N591" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R591" t="inlineStr">
         <is>
-          <t>FISEROVA Tereza</t>
-        </is>
-      </c>
-      <c r="U591" t="inlineStr">
-        <is>
-          <t>42016</t>
+          <t>SATILA Ana</t>
+        </is>
+      </c>
+      <c r="X591" t="inlineStr">
+        <is>
+          <t>35327</t>
         </is>
       </c>
     </row>
@@ -34801,38 +34841,38 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>12:26:00</t>
+          <t>12:29:00</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="J592" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K592" t="n">
         <v>591</v>
       </c>
       <c r="M592" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N592" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R592" t="inlineStr">
         <is>
-          <t>SATILA Ana</t>
-        </is>
-      </c>
-      <c r="U592" t="inlineStr">
-        <is>
-          <t>35327</t>
+          <t>FOX Jessica</t>
+        </is>
+      </c>
+      <c r="X592" t="inlineStr">
+        <is>
+          <t>36526</t>
         </is>
       </c>
     </row>
@@ -34869,45 +34909,35 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>12:29:00</t>
+          <t>12:32:00</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="J593" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K593" t="n">
         <v>592</v>
       </c>
-      <c r="M593" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N593" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R593" t="inlineStr">
         <is>
-          <t>FOX Jessica</t>
-        </is>
-      </c>
-      <c r="U593" t="inlineStr">
-        <is>
-          <t>36526</t>
+          <t>WOODS Kimberley</t>
+        </is>
+      </c>
+      <c r="X593" t="inlineStr">
+        <is>
+          <t>35650</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -34917,7 +34947,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
@@ -34937,28 +34967,38 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>12:32:00</t>
+          <t>12:40:01</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="J594" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K594" t="n">
         <v>593</v>
       </c>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N594" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R594" t="inlineStr">
         <is>
-          <t>WOODS Kimberley</t>
-        </is>
-      </c>
-      <c r="U594" t="inlineStr">
-        <is>
-          <t>35650</t>
+          <t>POPIELA Dariusz</t>
+        </is>
+      </c>
+      <c r="X594" t="inlineStr">
+        <is>
+          <t>35096</t>
         </is>
       </c>
     </row>
@@ -34995,7 +35035,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>12:40:01</t>
+          <t>12:43:00</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -35004,29 +35044,29 @@
         </is>
       </c>
       <c r="J595" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K595" t="n">
         <v>594</v>
       </c>
       <c r="M595" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N595" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R595" t="inlineStr">
         <is>
-          <t>POPIELA Dariusz</t>
-        </is>
-      </c>
-      <c r="U595" t="inlineStr">
-        <is>
-          <t>35096</t>
+          <t>PASIUT Michal</t>
+        </is>
+      </c>
+      <c r="X595" t="inlineStr">
+        <is>
+          <t>35095</t>
         </is>
       </c>
     </row>
@@ -35063,38 +35103,38 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>12:43:00</t>
+          <t>12:45:59</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J596" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K596" t="n">
         <v>595</v>
       </c>
       <c r="M596" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N596" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R596" t="inlineStr">
         <is>
-          <t>PASIUT Michal</t>
-        </is>
-      </c>
-      <c r="U596" t="inlineStr">
-        <is>
-          <t>35095</t>
+          <t>HRADILEK Vavrinec</t>
+        </is>
+      </c>
+      <c r="X596" t="inlineStr">
+        <is>
+          <t>35031</t>
         </is>
       </c>
     </row>
@@ -35131,38 +35171,38 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>12:45:59</t>
+          <t>12:49:01</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="J597" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K597" t="n">
         <v>596</v>
       </c>
       <c r="M597" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N597" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R597" t="inlineStr">
         <is>
-          <t>HRADILEK Vavrinec</t>
-        </is>
-      </c>
-      <c r="U597" t="inlineStr">
-        <is>
-          <t>35031</t>
+          <t>ADACHI Kazuya</t>
+        </is>
+      </c>
+      <c r="X597" t="inlineStr">
+        <is>
+          <t>36646</t>
         </is>
       </c>
     </row>
@@ -35199,38 +35239,38 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>12:49:01</t>
+          <t>12:51:58</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>SLO</t>
         </is>
       </c>
       <c r="J598" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="K598" t="n">
         <v>597</v>
       </c>
       <c r="M598" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N598" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R598" t="inlineStr">
         <is>
-          <t>ADACHI Kazuya</t>
-        </is>
-      </c>
-      <c r="U598" t="inlineStr">
-        <is>
-          <t>36646</t>
+          <t>KAUZER Peter</t>
+        </is>
+      </c>
+      <c r="X598" t="inlineStr">
+        <is>
+          <t>35589</t>
         </is>
       </c>
     </row>
@@ -35267,38 +35307,38 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>12:51:58</t>
+          <t>12:56:59</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J599" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K599" t="n">
         <v>598</v>
       </c>
       <c r="M599" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N599" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R599" t="inlineStr">
         <is>
-          <t>KAUZER Peter</t>
-        </is>
-      </c>
-      <c r="U599" t="inlineStr">
-        <is>
-          <t>35589</t>
+          <t>PRINDIS Vit</t>
+        </is>
+      </c>
+      <c r="X599" t="inlineStr">
+        <is>
+          <t>35065</t>
         </is>
       </c>
     </row>
@@ -35335,38 +35375,38 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>12:56:59</t>
+          <t>12:59:59</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="J600" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K600" t="n">
         <v>599</v>
       </c>
       <c r="M600" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N600" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R600" t="inlineStr">
         <is>
-          <t>PRINDIS Vit</t>
-        </is>
-      </c>
-      <c r="U600" t="inlineStr">
-        <is>
-          <t>35065</t>
+          <t>CLARKE Joseph</t>
+        </is>
+      </c>
+      <c r="X600" t="inlineStr">
+        <is>
+          <t>35654</t>
         </is>
       </c>
     </row>
@@ -35403,38 +35443,38 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>12:59:59</t>
+          <t>13:03:01</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J601" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K601" t="n">
         <v>600</v>
       </c>
       <c r="M601" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N601" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R601" t="inlineStr">
         <is>
-          <t>CLARKE Joseph</t>
-        </is>
-      </c>
-      <c r="U601" t="inlineStr">
-        <is>
-          <t>35654</t>
+          <t>NEVEU Boris</t>
+        </is>
+      </c>
+      <c r="X601" t="inlineStr">
+        <is>
+          <t>35396</t>
         </is>
       </c>
     </row>
@@ -35471,38 +35511,38 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>13:03:01</t>
+          <t>13:05:58</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J602" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K602" t="n">
         <v>601</v>
       </c>
       <c r="M602" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N602" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R602" t="inlineStr">
         <is>
-          <t>NEVEU Boris</t>
-        </is>
-      </c>
-      <c r="U602" t="inlineStr">
-        <is>
-          <t>35396</t>
+          <t>PRSKAVEC Jiri</t>
+        </is>
+      </c>
+      <c r="X602" t="inlineStr">
+        <is>
+          <t>35033</t>
         </is>
       </c>
     </row>
@@ -35539,45 +35579,45 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>13:05:58</t>
+          <t>13:08:58</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="J603" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K603" t="n">
         <v>602</v>
       </c>
       <c r="M603" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N603" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R603" t="inlineStr">
         <is>
-          <t>PRSKAVEC Jiri</t>
-        </is>
-      </c>
-      <c r="U603" t="inlineStr">
-        <is>
-          <t>35033</t>
+          <t>DE GENNARO Giovanni</t>
+        </is>
+      </c>
+      <c r="X603" t="inlineStr">
+        <is>
+          <t>35244</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -35587,7 +35627,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
@@ -35607,38 +35647,38 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>13:08:58</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J604" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K604" t="n">
         <v>603</v>
       </c>
-      <c r="M604" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="N604" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="R604" t="inlineStr">
         <is>
-          <t>DE GENNARO Giovanni</t>
-        </is>
-      </c>
-      <c r="U604" t="inlineStr">
-        <is>
-          <t>35244</t>
+          <t>GALUSKOVA Antonie</t>
+        </is>
+      </c>
+      <c r="S604" t="inlineStr">
+        <is>
+          <t>HEGER Vojtech</t>
+        </is>
+      </c>
+      <c r="X604" t="inlineStr">
+        <is>
+          <t>68754</t>
+        </is>
+      </c>
+      <c r="Y604" t="inlineStr">
+        <is>
+          <t>68872</t>
         </is>
       </c>
     </row>
@@ -35675,38 +35715,38 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>13:52:00</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J605" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K605" t="n">
         <v>604</v>
       </c>
       <c r="R605" t="inlineStr">
         <is>
-          <t>GALUSKOVA Antonie</t>
+          <t>GOTTOWIK Marie</t>
         </is>
       </c>
       <c r="S605" t="inlineStr">
         <is>
-          <t>HEGER Vojtech</t>
-        </is>
-      </c>
-      <c r="U605" t="inlineStr">
-        <is>
-          <t>68754</t>
-        </is>
-      </c>
-      <c r="V605" t="inlineStr">
-        <is>
-          <t>68872</t>
+          <t>PIONTEK Jeffrey</t>
+        </is>
+      </c>
+      <c r="X605" t="inlineStr">
+        <is>
+          <t>102017</t>
+        </is>
+      </c>
+      <c r="Y605" t="inlineStr">
+        <is>
+          <t>93814</t>
         </is>
       </c>
     </row>
@@ -35743,38 +35783,38 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>13:52:00</t>
+          <t>13:54:00</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J606" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K606" t="n">
         <v>605</v>
       </c>
       <c r="R606" t="inlineStr">
         <is>
-          <t>GOTTOWIK Marie</t>
+          <t>VOJTOVA Veronika</t>
         </is>
       </c>
       <c r="S606" t="inlineStr">
         <is>
-          <t>PIONTEK Jeffrey</t>
-        </is>
-      </c>
-      <c r="U606" t="inlineStr">
-        <is>
-          <t>102017</t>
-        </is>
-      </c>
-      <c r="V606" t="inlineStr">
-        <is>
-          <t>93814</t>
+          <t>MASEK Jan</t>
+        </is>
+      </c>
+      <c r="X606" t="inlineStr">
+        <is>
+          <t>35945</t>
+        </is>
+      </c>
+      <c r="Y606" t="inlineStr">
+        <is>
+          <t>36013</t>
         </is>
       </c>
     </row>
@@ -35811,7 +35851,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>13:54:00</t>
+          <t>13:56:00</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -35820,90 +35860,22 @@
         </is>
       </c>
       <c r="J607" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K607" t="n">
         <v>606</v>
       </c>
       <c r="R607" t="inlineStr">
         <is>
-          <t>VOJTOVA Veronika</t>
+          <t>FISEROVA Tereza</t>
         </is>
       </c>
       <c r="S607" t="inlineStr">
         <is>
-          <t>MASEK Jan</t>
-        </is>
-      </c>
-      <c r="U607" t="inlineStr">
-        <is>
-          <t>35945</t>
-        </is>
-      </c>
-      <c r="V607" t="inlineStr">
-        <is>
-          <t>36013</t>
-        </is>
-      </c>
-    </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="B608" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C608" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E608" t="inlineStr">
-        <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="F608" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G608" t="inlineStr">
-        <is>
-          <t>2019-09-08</t>
-        </is>
-      </c>
-      <c r="H608" t="inlineStr">
-        <is>
-          <t>13:56:00</t>
-        </is>
-      </c>
-      <c r="I608" t="inlineStr">
-        <is>
-          <t>CZE</t>
-        </is>
-      </c>
-      <c r="J608" t="n">
-        <v>1</v>
-      </c>
-      <c r="K608" t="n">
-        <v>607</v>
-      </c>
-      <c r="R608" t="inlineStr">
-        <is>
-          <t>FISEROVA Tereza</t>
-        </is>
-      </c>
-      <c r="S608" t="inlineStr">
-        <is>
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="V608" t="inlineStr">
+      <c r="Y607" t="inlineStr">
         <is>
           <t>35061</t>
         </is>

--- a/events/Prague_2019_WC/Prague_2019_WC_start.xlsx
+++ b/events/Prague_2019_WC/Prague_2019_WC_start.xlsx
@@ -35875,6 +35875,11 @@
           <t>JANE Jakub</t>
         </is>
       </c>
+      <c r="X607" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
       <c r="Y607" t="inlineStr">
         <is>
           <t>35061</t>
